--- a/rag-mcp/data/corporate/seojun_roasters/sustainability_report.xlsx
+++ b/rag-mcp/data/corporate/seojun_roasters/sustainability_report.xlsx
@@ -367,7 +367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="1" min="1" max="1"/>
@@ -391,40 +391,30 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>company_id</t>
+          <t>document_type</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>document_id</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>section</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>content</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>section</t>
+          <t>source_url</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="H1" s="9" t="inlineStr">
-        <is>
-          <t>source_url</t>
-        </is>
-      </c>
-      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>published_at</t>
         </is>
@@ -438,36 +428,26 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters</t>
+          <t>sustainability_report</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters-sustainability_report</t>
+          <t>서준로스터스 지속가능경영보고서</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>sustainability_report</t>
+          <t>보고 범위</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>서준로스터스 지속가능경영보고서</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>보고 범위</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
           <t>이 보고서는 서준로스터스의 환경·지역사회 분야 추진 방향을 담는다. 절감량·기부·매장별 성과 수치는 포함하지 않으며 목표와 이행을 구분한다.</t>
         </is>
       </c>
-      <c r="H2" s="7" t="str"/>
-      <c r="I2" s="7" t="str"/>
+      <c r="F2" s="7" t="str"/>
+      <c r="G2" s="7" t="str"/>
     </row>
     <row r="3" ht="130" customHeight="1" s="1">
       <c r="A3" s="7" t="inlineStr">
@@ -477,36 +457,26 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters</t>
+          <t>sustainability_report</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters-sustainability_report</t>
+          <t>서준로스터스 지속가능경영보고서</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>sustainability_report</t>
+          <t>다회용기·폐기물</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>서준로스터스 지속가능경영보고서</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>다회용기·폐기물</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
           <t>다회용기 사용과 불필요한 일회용품 감소를 지향한다. 일부 매장 시도를 전 매장의 완전한 무폐기 운영으로 광고하지 않는다.</t>
         </is>
       </c>
-      <c r="H3" s="7" t="str"/>
-      <c r="I3" s="7" t="str"/>
+      <c r="F3" s="7" t="str"/>
+      <c r="G3" s="7" t="str"/>
     </row>
     <row r="4" ht="130" customHeight="1" s="1">
       <c r="A4" s="7" t="inlineStr">
@@ -516,36 +486,26 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters</t>
+          <t>sustainability_report</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>seojun_roasters-sustainability_report</t>
+          <t>서준로스터스 지속가능경영보고서</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>sustainability_report</t>
+          <t>원두 조달</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>서준로스터스 지속가능경영보고서</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>원두 조달</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
           <t>거래 업체의 관련 자료를 확인하는 절차 마련을 지향한다. 모든 농장의 아동노동 부재를 확인한 실사 기록이나 인증서는 제공하지 않는다.</t>
         </is>
       </c>
-      <c r="H4" s="7" t="str"/>
-      <c r="I4" s="7" t="str"/>
+      <c r="F4" s="7" t="str"/>
+      <c r="G4" s="7" t="str"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
